--- a/public/menu-import-template.xlsx
+++ b/public/menu-import-template.xlsx
@@ -932,12 +932,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Fresh Lime Soda</t>
+          <t>Sweet Lime Soda</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Lime Soda</t>
+          <t>Sweet Lime</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
